--- a/data/master_data.xlsx
+++ b/data/master_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZULFAA\BPS\Scrapping\monitoring-petugas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB85D65D-46AE-4F06-8D9A-88AD17C97422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898FB173-708E-453C-A1BB-6BB9751412DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{86094A76-1351-45B9-BE64-2436059B6A37}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86094A76-1351-45B9-BE64-2436059B6A37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3834,12 +3834,6 @@
     <t>8171030013003402</t>
   </si>
   <si>
-    <t>8171030013200101</t>
-  </si>
-  <si>
-    <t>8171030014000102</t>
-  </si>
-  <si>
     <t>8171030013002801</t>
   </si>
   <si>
@@ -3877,6 +3871,12 @@
   </si>
   <si>
     <t>uchyjuve@gmail.com</t>
+  </si>
+  <si>
+    <t>8171030014000100</t>
+  </si>
+  <si>
+    <t>8171030013200100</t>
   </si>
 </sst>
 </file>
@@ -26195,7 +26195,7 @@
         <v>1056</v>
       </c>
       <c r="I626" s="5" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J626" s="3" t="s">
         <v>1057</v>
@@ -26230,7 +26230,7 @@
         <v>1056</v>
       </c>
       <c r="I627" s="5" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J627" s="3" t="s">
         <v>1057</v>
@@ -26265,7 +26265,7 @@
         <v>1056</v>
       </c>
       <c r="I628" s="5" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J628" s="3" t="s">
         <v>1057</v>
@@ -26300,7 +26300,7 @@
         <v>1056</v>
       </c>
       <c r="I629" s="5" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J629" s="3" t="s">
         <v>1057</v>
@@ -26335,7 +26335,7 @@
         <v>1056</v>
       </c>
       <c r="I630" s="5" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J630" s="3" t="s">
         <v>1057</v>
@@ -26370,7 +26370,7 @@
         <v>1056</v>
       </c>
       <c r="I631" s="5" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J631" s="3" t="s">
         <v>1057</v>
@@ -41431,7 +41431,7 @@
     </row>
     <row r="1062" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1062" s="6" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B1062" s="3" t="s">
         <v>1035</v>
@@ -41466,7 +41466,7 @@
     </row>
     <row r="1063" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1063" s="6" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B1063" s="3" t="s">
         <v>1035</v>
@@ -41746,7 +41746,7 @@
     </row>
     <row r="1071" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1071" s="6" t="s">
-        <v>1266</v>
+        <v>1280</v>
       </c>
       <c r="B1071" s="3" t="s">
         <v>1035</v>
@@ -41781,7 +41781,7 @@
     </row>
     <row r="1072" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1072" s="6" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
       <c r="B1072" s="3" t="s">
         <v>1035</v>
@@ -48081,7 +48081,7 @@
     </row>
     <row r="1252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1252" s="6" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B1252" s="3" t="s">
         <v>1035</v>
@@ -48116,7 +48116,7 @@
     </row>
     <row r="1253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1253" s="6" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B1253" s="3" t="s">
         <v>1035</v>
@@ -48186,7 +48186,7 @@
     </row>
     <row r="1255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1255" s="6" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B1255" s="3" t="s">
         <v>1035</v>
@@ -48221,7 +48221,7 @@
     </row>
     <row r="1256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1256" s="6" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B1256" s="3" t="s">
         <v>1035</v>
@@ -48256,7 +48256,7 @@
     </row>
     <row r="1257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1257" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B1257" s="3" t="s">
         <v>1035</v>
@@ -49551,7 +49551,7 @@
     </row>
     <row r="1294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1294" s="6" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B1294" s="3" t="s">
         <v>1035</v>
@@ -49586,7 +49586,7 @@
     </row>
     <row r="1295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1295" s="6" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B1295" s="3" t="s">
         <v>1035</v>
@@ -49621,7 +49621,7 @@
     </row>
     <row r="1296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1296" s="6" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B1296" s="3" t="s">
         <v>1035</v>
@@ -49656,7 +49656,7 @@
     </row>
     <row r="1297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1297" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B1297" s="3" t="s">
         <v>1035</v>
@@ -49691,7 +49691,7 @@
     </row>
     <row r="1298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1298" s="6" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B1298" s="3" t="s">
         <v>1035</v>

--- a/data/master_data.xlsx
+++ b/data/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZULFAA\BPS\Scrapping\monitoring-petugas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320CE2F6-B44D-4604-8F74-B863CAEE7FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098CFFB3-7AAA-498A-B8C1-9676A5830B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{86094A76-1351-45B9-BE64-2436059B6A37}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86094A76-1351-45B9-BE64-2436059B6A37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6715,11 +6715,11 @@
       <c r="G69" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="H69" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>276</v>
@@ -52060,38 +52060,38 @@
     <hyperlink ref="I626" r:id="rId3" xr:uid="{90693E4F-0939-4A86-A2E4-488310A27422}"/>
     <hyperlink ref="I627:I631" r:id="rId4" display="uchyjuve@gmail.com" xr:uid="{EAD25823-B47F-493D-A010-D2213BB2549D}"/>
     <hyperlink ref="I87" r:id="rId5" xr:uid="{D8C552A8-3A1E-4366-BB5D-CCEED3B2E471}"/>
-    <hyperlink ref="H69" r:id="rId6" xr:uid="{C39EB78B-F3FB-4C6D-9BD3-73DB0E6AD029}"/>
-    <hyperlink ref="I89" r:id="rId7" xr:uid="{259CFC0C-1793-45F8-A752-D34E0C3C2CC8}"/>
-    <hyperlink ref="I97" r:id="rId8" xr:uid="{FE7AF5CE-4C21-4C6D-8671-EE203F7A8FCD}"/>
-    <hyperlink ref="I307" r:id="rId9" xr:uid="{ADC3A9DA-20AA-495A-BCB8-F7CA0BB69A69}"/>
-    <hyperlink ref="I334" r:id="rId10" xr:uid="{417FD4D6-C0F9-48CE-8252-221D16DA695D}"/>
-    <hyperlink ref="I335" r:id="rId11" xr:uid="{45AFCCED-52FD-4B50-8FAE-02980CA071E3}"/>
-    <hyperlink ref="I340" r:id="rId12" xr:uid="{1D2FBD30-E837-443F-8B63-24759ECDCBC3}"/>
-    <hyperlink ref="I341" r:id="rId13" xr:uid="{93FEAFE6-8A8D-4C10-AFD3-04B19779D982}"/>
-    <hyperlink ref="I431" r:id="rId14" xr:uid="{9436DC5B-5501-4686-91D9-50442B4EC2F7}"/>
-    <hyperlink ref="I432" r:id="rId15" xr:uid="{90319334-3DA1-4811-BC9B-79A274CDBE10}"/>
-    <hyperlink ref="I450" r:id="rId16" xr:uid="{D618F2C3-B9A5-412F-BAC9-73A0ABA1A545}"/>
-    <hyperlink ref="I451" r:id="rId17" xr:uid="{A026EF9E-1A91-4CAB-B8B6-DB593595B607}"/>
-    <hyperlink ref="I452" r:id="rId18" xr:uid="{0F686A51-A1BD-4EEB-989F-9F3A961BD0C2}"/>
-    <hyperlink ref="I453" r:id="rId19" xr:uid="{89D87853-8D22-405A-BE5A-1AD9852B8F89}"/>
-    <hyperlink ref="I460" r:id="rId20" xr:uid="{241CC3EC-A192-4BE9-BC18-4365773D3C0A}"/>
-    <hyperlink ref="I469" r:id="rId21" xr:uid="{A7010415-0A0F-4F82-B6EE-515EC6E81DC6}"/>
-    <hyperlink ref="I499" r:id="rId22" xr:uid="{02B5B8DB-6A8B-4DCB-95A2-47A0696425E5}"/>
-    <hyperlink ref="I500" r:id="rId23" xr:uid="{B8796123-07E4-4988-B939-5CDE42910D9E}"/>
-    <hyperlink ref="I501" r:id="rId24" xr:uid="{203C2474-202D-4BE1-9F5F-6F1BAD88E429}"/>
-    <hyperlink ref="I513" r:id="rId25" xr:uid="{D602486D-18D4-4E2A-B01C-0CC370C25105}"/>
-    <hyperlink ref="I515" r:id="rId26" xr:uid="{4311FE58-DBF3-4DE3-9F35-51D5DF5E0034}"/>
-    <hyperlink ref="I516" r:id="rId27" xr:uid="{9E755045-1171-42FA-99FF-CA8D8925C17F}"/>
-    <hyperlink ref="I530" r:id="rId28" xr:uid="{80D8CFB1-B4A1-40B4-BA6D-FCB6CC7D549B}"/>
-    <hyperlink ref="I531" r:id="rId29" xr:uid="{A8A4CE92-619E-41C3-BE12-4F47965C0320}"/>
-    <hyperlink ref="I620" r:id="rId30" xr:uid="{C775C323-C92E-4991-845F-67CF7270A601}"/>
-    <hyperlink ref="I636" r:id="rId31" xr:uid="{760BDB43-0BD3-4875-B644-BE6808B85754}"/>
-    <hyperlink ref="I641" r:id="rId32" xr:uid="{EE023B74-9EE6-4CD6-AD57-39186D30FA9C}"/>
-    <hyperlink ref="I689" r:id="rId33" xr:uid="{DB894316-4166-4319-8113-C4152ECBD3DF}"/>
-    <hyperlink ref="I693" r:id="rId34" xr:uid="{6335BE41-E6AF-43EE-ABFA-95619D825639}"/>
-    <hyperlink ref="I719" r:id="rId35" xr:uid="{882A074C-FD64-4853-BBAC-4176E278D51A}"/>
-    <hyperlink ref="I1197" r:id="rId36" xr:uid="{F9B6DE5F-B058-496C-8F4E-7820987E23E4}"/>
-    <hyperlink ref="I1201" r:id="rId37" xr:uid="{DA69109F-920D-4956-A58C-283A63389DB1}"/>
+    <hyperlink ref="I89" r:id="rId6" xr:uid="{259CFC0C-1793-45F8-A752-D34E0C3C2CC8}"/>
+    <hyperlink ref="I97" r:id="rId7" xr:uid="{FE7AF5CE-4C21-4C6D-8671-EE203F7A8FCD}"/>
+    <hyperlink ref="I307" r:id="rId8" xr:uid="{ADC3A9DA-20AA-495A-BCB8-F7CA0BB69A69}"/>
+    <hyperlink ref="I334" r:id="rId9" xr:uid="{417FD4D6-C0F9-48CE-8252-221D16DA695D}"/>
+    <hyperlink ref="I335" r:id="rId10" xr:uid="{45AFCCED-52FD-4B50-8FAE-02980CA071E3}"/>
+    <hyperlink ref="I340" r:id="rId11" xr:uid="{1D2FBD30-E837-443F-8B63-24759ECDCBC3}"/>
+    <hyperlink ref="I341" r:id="rId12" xr:uid="{93FEAFE6-8A8D-4C10-AFD3-04B19779D982}"/>
+    <hyperlink ref="I431" r:id="rId13" xr:uid="{9436DC5B-5501-4686-91D9-50442B4EC2F7}"/>
+    <hyperlink ref="I432" r:id="rId14" xr:uid="{90319334-3DA1-4811-BC9B-79A274CDBE10}"/>
+    <hyperlink ref="I450" r:id="rId15" xr:uid="{D618F2C3-B9A5-412F-BAC9-73A0ABA1A545}"/>
+    <hyperlink ref="I451" r:id="rId16" xr:uid="{A026EF9E-1A91-4CAB-B8B6-DB593595B607}"/>
+    <hyperlink ref="I452" r:id="rId17" xr:uid="{0F686A51-A1BD-4EEB-989F-9F3A961BD0C2}"/>
+    <hyperlink ref="I453" r:id="rId18" xr:uid="{89D87853-8D22-405A-BE5A-1AD9852B8F89}"/>
+    <hyperlink ref="I460" r:id="rId19" xr:uid="{241CC3EC-A192-4BE9-BC18-4365773D3C0A}"/>
+    <hyperlink ref="I469" r:id="rId20" xr:uid="{A7010415-0A0F-4F82-B6EE-515EC6E81DC6}"/>
+    <hyperlink ref="I499" r:id="rId21" xr:uid="{02B5B8DB-6A8B-4DCB-95A2-47A0696425E5}"/>
+    <hyperlink ref="I500" r:id="rId22" xr:uid="{B8796123-07E4-4988-B939-5CDE42910D9E}"/>
+    <hyperlink ref="I501" r:id="rId23" xr:uid="{203C2474-202D-4BE1-9F5F-6F1BAD88E429}"/>
+    <hyperlink ref="I513" r:id="rId24" xr:uid="{D602486D-18D4-4E2A-B01C-0CC370C25105}"/>
+    <hyperlink ref="I515" r:id="rId25" xr:uid="{4311FE58-DBF3-4DE3-9F35-51D5DF5E0034}"/>
+    <hyperlink ref="I516" r:id="rId26" xr:uid="{9E755045-1171-42FA-99FF-CA8D8925C17F}"/>
+    <hyperlink ref="I530" r:id="rId27" xr:uid="{80D8CFB1-B4A1-40B4-BA6D-FCB6CC7D549B}"/>
+    <hyperlink ref="I531" r:id="rId28" xr:uid="{A8A4CE92-619E-41C3-BE12-4F47965C0320}"/>
+    <hyperlink ref="I620" r:id="rId29" xr:uid="{C775C323-C92E-4991-845F-67CF7270A601}"/>
+    <hyperlink ref="I636" r:id="rId30" xr:uid="{760BDB43-0BD3-4875-B644-BE6808B85754}"/>
+    <hyperlink ref="I641" r:id="rId31" xr:uid="{EE023B74-9EE6-4CD6-AD57-39186D30FA9C}"/>
+    <hyperlink ref="I689" r:id="rId32" xr:uid="{DB894316-4166-4319-8113-C4152ECBD3DF}"/>
+    <hyperlink ref="I693" r:id="rId33" xr:uid="{6335BE41-E6AF-43EE-ABFA-95619D825639}"/>
+    <hyperlink ref="I719" r:id="rId34" xr:uid="{882A074C-FD64-4853-BBAC-4176E278D51A}"/>
+    <hyperlink ref="I1197" r:id="rId35" xr:uid="{F9B6DE5F-B058-496C-8F4E-7820987E23E4}"/>
+    <hyperlink ref="I1201" r:id="rId36" xr:uid="{DA69109F-920D-4956-A58C-283A63389DB1}"/>
+    <hyperlink ref="I69" r:id="rId37" xr:uid="{273849BE-B3B2-4C85-923A-A61A1903ABFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/master_data.xlsx
+++ b/data/master_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZULFAA\BPS\Scrapping\monitoring-petugas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098CFFB3-7AAA-498A-B8C1-9676A5830B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DF7D66-358A-464C-B4C8-0980F23E0E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86094A76-1351-45B9-BE64-2436059B6A37}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13841" uniqueCount="1282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13841" uniqueCount="1281">
   <si>
     <t>natasialatuhihin0@gmail.com</t>
   </si>
@@ -3865,9 +3865,6 @@
   </si>
   <si>
     <t>Vitriansye Chelia Ivone Dacosta</t>
-  </si>
-  <si>
-    <t>Benoni Andre</t>
   </si>
   <si>
     <t>rhalyvuja54@gmail.com</t>
@@ -19427,7 +19424,7 @@
         <v>66</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1277</v>
+        <v>538</v>
       </c>
       <c r="K432" s="3" t="s">
         <v>520</v>
@@ -20057,7 +20054,7 @@
         <v>66</v>
       </c>
       <c r="J450" s="3" t="s">
-        <v>1277</v>
+        <v>538</v>
       </c>
       <c r="K450" s="3" t="s">
         <v>520</v>
@@ -20089,10 +20086,10 @@
         <v>1044</v>
       </c>
       <c r="I451" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J451" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="J451" s="3" t="s">
-        <v>1279</v>
       </c>
       <c r="K451" s="3" t="s">
         <v>520</v>
@@ -20124,10 +20121,10 @@
         <v>1044</v>
       </c>
       <c r="I452" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J452" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="J452" s="3" t="s">
-        <v>1279</v>
       </c>
       <c r="K452" s="3" t="s">
         <v>520</v>
@@ -20159,10 +20156,10 @@
         <v>1044</v>
       </c>
       <c r="I453" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J453" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="J453" s="3" t="s">
-        <v>1279</v>
       </c>
       <c r="K453" s="3" t="s">
         <v>520</v>
@@ -46234,10 +46231,10 @@
         <v>1066</v>
       </c>
       <c r="I1198" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1198" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1198" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1198" s="3" t="s">
         <v>958</v>
@@ -46269,10 +46266,10 @@
         <v>1066</v>
       </c>
       <c r="I1199" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1199" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1199" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1199" s="3" t="s">
         <v>958</v>
@@ -46304,10 +46301,10 @@
         <v>1066</v>
       </c>
       <c r="I1200" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1200" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1200" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1200" s="3" t="s">
         <v>958</v>
@@ -48229,10 +48226,10 @@
         <v>1067</v>
       </c>
       <c r="I1255" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J1255" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="J1255" s="3" t="s">
-        <v>1279</v>
       </c>
       <c r="K1255" s="3" t="s">
         <v>990</v>
@@ -48264,10 +48261,10 @@
         <v>1067</v>
       </c>
       <c r="I1256" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J1256" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="J1256" s="3" t="s">
-        <v>1279</v>
       </c>
       <c r="K1256" s="3" t="s">
         <v>990</v>
@@ -48299,10 +48296,10 @@
         <v>1067</v>
       </c>
       <c r="I1257" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J1257" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="J1257" s="3" t="s">
-        <v>1279</v>
       </c>
       <c r="K1257" s="3" t="s">
         <v>990</v>
@@ -48334,10 +48331,10 @@
         <v>1067</v>
       </c>
       <c r="I1258" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1258" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1258" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1258" s="3" t="s">
         <v>990</v>
@@ -48369,10 +48366,10 @@
         <v>1067</v>
       </c>
       <c r="I1259" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1259" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1259" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1259" s="3" t="s">
         <v>990</v>
@@ -48404,10 +48401,10 @@
         <v>1067</v>
       </c>
       <c r="I1260" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1260" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1260" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1260" s="3" t="s">
         <v>990</v>
@@ -48439,10 +48436,10 @@
         <v>1067</v>
       </c>
       <c r="I1261" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1261" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1261" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1261" s="3" t="s">
         <v>990</v>
@@ -48789,10 +48786,10 @@
         <v>1067</v>
       </c>
       <c r="I1271" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J1271" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="J1271" s="3" t="s">
-        <v>1281</v>
       </c>
       <c r="K1271" s="3" t="s">
         <v>990</v>
